--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103633678</v>
+        <v>104155385</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584130.4826642105</v>
+        <v>584039</v>
       </c>
       <c r="R2" t="n">
-        <v>7047608.911248453</v>
+        <v>7047814</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-18</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-18</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,12 +786,7 @@
         <v>103633885</v>
       </c>
       <c r="B3" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,12 +803,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584074.6993439808</v>
+        <v>584075</v>
       </c>
       <c r="R3" t="n">
-        <v>7047590.038240715</v>
+        <v>7047590</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +852,9 @@
           <t>2022-09-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103633624</v>
+        <v>104160881</v>
       </c>
       <c r="B4" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +892,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584121.046283897</v>
+        <v>584146</v>
       </c>
       <c r="R4" t="n">
-        <v>7047644.794581138</v>
+        <v>7047543</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,22 +947,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-18</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-18</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,37 +989,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104161921</v>
+        <v>104161644</v>
       </c>
       <c r="B5" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4365</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584051.1800139125</v>
+        <v>584080</v>
       </c>
       <c r="R5" t="n">
-        <v>7047617.966137786</v>
+        <v>7047594</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,7 +1060,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1070,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,37 +1097,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104157611</v>
+        <v>104161771</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584186.8050646301</v>
+        <v>584087</v>
       </c>
       <c r="R6" t="n">
-        <v>7047725.490950738</v>
+        <v>7047616</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104161928</v>
+        <v>104155697</v>
       </c>
       <c r="B7" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584051.1800139125</v>
+        <v>584094</v>
       </c>
       <c r="R7" t="n">
-        <v>7047617.966137786</v>
+        <v>7047817</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1316,7 +1276,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,37 +1313,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104160885</v>
+        <v>104161701</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1394,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584145.1734197424</v>
+        <v>584080</v>
       </c>
       <c r="R8" t="n">
-        <v>7047543.278129204</v>
+        <v>7047590</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1466,15 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104160881</v>
+        <v>104161488</v>
       </c>
       <c r="B9" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,21 +1432,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584145.1734197424</v>
+        <v>584067</v>
       </c>
       <c r="R9" t="n">
-        <v>7047543.278129204</v>
+        <v>7047577</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1542,7 +1492,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1552,7 +1502,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,15 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104161644</v>
+        <v>104155958</v>
       </c>
       <c r="B10" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584079.5033860218</v>
+        <v>584180</v>
       </c>
       <c r="R10" t="n">
-        <v>7047594.180088941</v>
+        <v>7047775</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1653,19 +1598,9 @@
           <t>2022-10-17</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:46</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,37 +1627,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104161701</v>
+        <v>104161902</v>
       </c>
       <c r="B11" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>4365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584079.609476297</v>
+        <v>584052</v>
       </c>
       <c r="R11" t="n">
-        <v>7047590.168076294</v>
+        <v>7047618</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1766,19 +1696,9 @@
           <t>2022-10-17</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>16:46</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>16:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,15 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104161771</v>
+        <v>115598818</v>
       </c>
       <c r="B12" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,38 +1736,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584087.4304313402</v>
+        <v>584042</v>
       </c>
       <c r="R12" t="n">
-        <v>7047615.355906496</v>
+        <v>7047727</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1876,22 +1790,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,66 +1820,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104157574</v>
+        <v>115600812</v>
       </c>
       <c r="B13" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584190.7160436618</v>
+        <v>584124</v>
       </c>
       <c r="R13" t="n">
-        <v>7047729.60916518</v>
+        <v>7047475</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1989,22 +1897,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,49 +1927,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104155958</v>
+        <v>104155987</v>
       </c>
       <c r="B14" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2072,10 +1975,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584179.2578471813</v>
+        <v>584193</v>
       </c>
       <c r="R14" t="n">
-        <v>7047774.358789326</v>
+        <v>7047771</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2107,7 +2010,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2020,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,37 +2047,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104161089</v>
+        <v>104161842</v>
       </c>
       <c r="B15" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2185,10 +2083,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584075.9810752656</v>
+        <v>584071</v>
       </c>
       <c r="R15" t="n">
-        <v>7047575.351090001</v>
+        <v>7047627</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2257,15 +2155,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104155621</v>
+        <v>104160594</v>
       </c>
       <c r="B16" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,21 +2166,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2298,10 +2191,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584095.9638854091</v>
+        <v>584262</v>
       </c>
       <c r="R16" t="n">
-        <v>7047799.364459976</v>
+        <v>7047511</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2333,7 +2226,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2236,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,15 +2263,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104161835</v>
+        <v>104369095</v>
       </c>
       <c r="B17" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2386,21 +2274,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2411,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584070.1500529887</v>
+        <v>584146</v>
       </c>
       <c r="R17" t="n">
-        <v>7047626.943302307</v>
+        <v>7047818</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2441,22 +2329,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2022-10-29</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2022-10-29</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2471,49 +2359,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104161842</v>
+        <v>103633678</v>
       </c>
       <c r="B18" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2524,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584070.1500529887</v>
+        <v>584130</v>
       </c>
       <c r="R18" t="n">
-        <v>7047626.943302307</v>
+        <v>7047609</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2554,22 +2437,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:46</t>
+          <t>2022-09-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:46</t>
+          <t>2022-09-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2596,37 +2469,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104161027</v>
+        <v>103634199</v>
       </c>
       <c r="B19" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2637,10 +2505,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584090.7940653766</v>
+        <v>584026</v>
       </c>
       <c r="R19" t="n">
-        <v>7047572.620153017</v>
+        <v>7047727</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2667,22 +2535,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:46</t>
+          <t>2022-09-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:46</t>
+          <t>2022-09-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2709,37 +2567,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104161488</v>
+        <v>103634296</v>
       </c>
       <c r="B20" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2750,10 +2603,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584067.8873450229</v>
+        <v>584038</v>
       </c>
       <c r="R20" t="n">
-        <v>7047577.367552139</v>
+        <v>7047762</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2780,22 +2633,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>16:25</t>
+          <t>2022-09-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>16:25</t>
+          <t>2022-09-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,15 +2670,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104155966</v>
+        <v>104155882</v>
       </c>
       <c r="B21" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,21 +2681,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2863,10 +2706,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584189.4220165391</v>
+        <v>584184</v>
       </c>
       <c r="R21" t="n">
-        <v>7047744.741332997</v>
+        <v>7047793</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2898,7 +2741,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2908,7 +2751,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2935,47 +2778,43 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115475818</v>
+        <v>104155991</v>
       </c>
       <c r="B22" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skumsåsberget (Skumsåsberget), Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584152</v>
+        <v>584193</v>
       </c>
       <c r="R22" t="n">
         <v>7047771</v>
@@ -3005,22 +2844,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3035,70 +2879,61 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115477919</v>
+        <v>104156221</v>
       </c>
       <c r="B23" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skumsåsberget (Skumsåsberget), Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584186</v>
+        <v>584208</v>
       </c>
       <c r="R23" t="n">
-        <v>7047481</v>
+        <v>7047743</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3122,22 +2957,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,65 +2992,61 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115478462</v>
+        <v>104160885</v>
       </c>
       <c r="B24" t="n">
-        <v>78246</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skumsåsberget (Skumsåsberget), Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584113</v>
+        <v>584146</v>
       </c>
       <c r="R24" t="n">
-        <v>7047657</v>
+        <v>7047543</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3234,22 +3070,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3264,70 +3100,61 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115477802</v>
+        <v>104369108</v>
       </c>
       <c r="B25" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skumsåsberget (Skumsåsberget), Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584205</v>
+        <v>584129</v>
       </c>
       <c r="R25" t="n">
-        <v>7047467</v>
+        <v>7047823</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3351,22 +3178,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2022-10-29</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2022-10-29</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3381,27 +3208,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115600902</v>
+        <v>103633624</v>
       </c>
       <c r="B26" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3409,42 +3231,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skumsåsberget (Skumsåsberget), Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584123</v>
+        <v>584121</v>
       </c>
       <c r="R26" t="n">
-        <v>7047482</v>
+        <v>7047645</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3468,22 +3286,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:48</t>
+          <t>2022-09-18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:48</t>
+          <t>2022-09-18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3498,27 +3306,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115600486</v>
+        <v>115478462</v>
       </c>
       <c r="B27" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3526,39 +3329,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skumsåsberget (Skumsåsberget), Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584098</v>
+        <v>584113</v>
       </c>
       <c r="R27" t="n">
-        <v>7047540</v>
+        <v>7047657</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3585,22 +3383,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3627,15 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115600812</v>
+        <v>104161089</v>
       </c>
       <c r="B28" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3643,37 +3436,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skumsåsberget (Skumsåsberget), Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584124</v>
+        <v>584076</v>
       </c>
       <c r="R28" t="n">
-        <v>7047475</v>
+        <v>7047575</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3697,22 +3491,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3727,27 +3521,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115601710</v>
+        <v>104161835</v>
       </c>
       <c r="B29" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3755,42 +3544,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skumsåsberget (Skumsåsberget), Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584185</v>
+        <v>584071</v>
       </c>
       <c r="R29" t="n">
-        <v>7047424</v>
+        <v>7047627</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3814,22 +3599,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3844,27 +3629,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>115598818</v>
+        <v>104161928</v>
       </c>
       <c r="B30" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3872,37 +3652,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skumsåsberget (Skumsåsberget), Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584042</v>
+        <v>584052</v>
       </c>
       <c r="R30" t="n">
-        <v>7047727</v>
+        <v>7047618</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3926,22 +3707,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3956,70 +3727,61 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>115600450</v>
+        <v>104157574</v>
       </c>
       <c r="B31" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skumsåsberget (Skumsåsberget), Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584104</v>
+        <v>584191</v>
       </c>
       <c r="R31" t="n">
-        <v>7047526</v>
+        <v>7047729</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4043,22 +3805,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4073,27 +3835,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115599859</v>
+        <v>115477802</v>
       </c>
       <c r="B32" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4121,19 +3878,19 @@
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skumsåsberget (Skumsåsberget), Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584084</v>
+        <v>584205</v>
       </c>
       <c r="R32" t="n">
-        <v>7047629</v>
+        <v>7047467</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4160,22 +3917,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4202,15 +3959,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115601916</v>
+        <v>115477919</v>
       </c>
       <c r="B33" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4243,14 +3995,14 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skumsåsberget (Skumsåsberget), Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584210</v>
+        <v>584186</v>
       </c>
       <c r="R33" t="n">
-        <v>7047396</v>
+        <v>7047481</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4277,22 +4029,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4319,15 +4071,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115601374</v>
+        <v>115598342</v>
       </c>
       <c r="B34" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4355,22 +4102,22 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skumsåsberget (Skumsåsberget), Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584149</v>
+        <v>584036</v>
       </c>
       <c r="R34" t="n">
-        <v>7047442</v>
+        <v>7047798</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4399,7 +4146,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4409,7 +4156,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4439,12 +4186,7 @@
         <v>115599470</v>
       </c>
       <c r="B35" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4477,7 +4219,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skumsåsberget (Skumsåsberget), Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
@@ -4550,6 +4292,1653 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>115599859</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>584084</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7047629</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>115600450</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>584104</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7047526</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jonatan Nordström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jonatan Nordström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>115600486</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>584098</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7047540</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>115600902</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>584123</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7047482</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>115601374</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>584149</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7047442</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>115601710</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>584185</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7047424</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>115601916</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>584210</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7047396</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>115604241</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>584185</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7047771</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>103634191</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>584026</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7047727</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2022-09-18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2022-09-18</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>104155621</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>584096</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7047800</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>104155966</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>584190</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7047745</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>104157121</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>584196</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7047725</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>104157530</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>584198</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7047725</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>104157571</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>584196</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7047731</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>104157611</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>584187</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7047726</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104155385</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103633885</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104160881</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104161644</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104161771</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104155697</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104161701</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1526,6 +1566,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104161488</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1624,6 +1669,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104155958</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104161902</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1829,6 +1884,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115598818</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1936,6 +1996,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115600812</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2044,6 +2109,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104155987</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2152,6 +2222,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104161842</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2260,6 +2335,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104160594</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2368,6 +2448,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104369095</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2466,6 +2551,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103633678</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2564,6 +2654,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103634199</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2667,6 +2762,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103634296</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2775,6 +2875,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104155882</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2888,6 +2993,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104155991</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3001,6 +3111,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104156221</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3109,6 +3224,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104160885</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3217,6 +3337,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104369108</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3315,6 +3440,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103633624</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3422,6 +3552,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115478462</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3530,6 +3665,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104161089</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3638,6 +3778,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104161835</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3736,6 +3881,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104161928</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3844,6 +3994,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104157574</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3956,6 +4111,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115477802</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4068,6 +4228,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115477919</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4180,6 +4345,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115598342</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4292,6 +4462,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115599470</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4404,6 +4579,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115599859</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4516,6 +4696,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115600450</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4628,6 +4813,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115600486</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4740,6 +4930,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115600902</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4852,6 +5047,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115601374</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4964,6 +5164,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115601710</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5076,6 +5281,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115601916</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5188,6 +5398,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115604241</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5291,6 +5506,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103634191</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5399,6 +5619,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104155621</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5507,6 +5732,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104155966</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5615,6 +5845,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104157121</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5723,6 +5958,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104157530</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5831,6 +6071,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104157571</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5939,8 +6184,64 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104157611</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>